--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 17,23</t>
+          <t>6,72; 16,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,23</t>
+          <t>-1,32; 9,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 1,94</t>
+          <t>-9,21; 1,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,78</t>
+          <t>1,25; 10,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,52</t>
+          <t>-2,26; 7,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,43; -12,13</t>
+          <t>-27,26; -12,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,83</t>
+          <t>5,08; 12,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 7,23</t>
+          <t>-0,22; 7,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -6,66</t>
+          <t>-16,15; -6,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,95; 37,42</t>
+          <t>13,38; 37,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 22,17</t>
+          <t>-2,5; 20,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 4,33</t>
+          <t>-18,15; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 17,91</t>
+          <t>1,91; 18,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 12,39</t>
+          <t>-3,49; 12,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -19,56</t>
+          <t>-43,33; -19,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 23,77</t>
+          <t>8,87; 23,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 13,28</t>
+          <t>-0,4; 13,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -12,54</t>
+          <t>-28,39; -12,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,43</t>
+          <t>0,51; 9,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,46</t>
+          <t>-1,74; 7,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,31; -5,49</t>
+          <t>-35,04; -5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,57</t>
+          <t>1,81; 10,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,74</t>
+          <t>-4,09; 4,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -11,35</t>
+          <t>-19,8; -11,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,85</t>
+          <t>2,79; 9,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,68</t>
+          <t>-1,27; 5,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -10,42</t>
+          <t>-30,45; -10,45</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 22,89</t>
+          <t>1,22; 21,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 16,22</t>
+          <t>-3,48; 15,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,35; -11,45</t>
+          <t>-69,68; -12,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 16,79</t>
+          <t>2,7; 16,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,61</t>
+          <t>-6,1; 7,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -18,21</t>
+          <t>-29,35; -18,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 15,99</t>
+          <t>4,72; 16,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 8,5</t>
+          <t>-2,17; 9,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -18,44</t>
+          <t>-53,01; -18,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,4</t>
+          <t>-4,91; 6,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,96</t>
+          <t>-6,57; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -2,59</t>
+          <t>-13,62; -2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,76</t>
+          <t>-0,84; 8,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 1,73</t>
+          <t>-8,56; 1,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 12,24</t>
+          <t>-24,19; 14,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,95</t>
+          <t>-1,08; 6,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,49</t>
+          <t>-6,16; 1,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 9,28</t>
+          <t>-16,3; 8,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 13,46</t>
+          <t>-9,35; 14,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 10,4</t>
+          <t>-12,47; 10,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -5,21</t>
+          <t>-26,12; -4,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 14,42</t>
+          <t>-1,42; 13,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 2,79</t>
+          <t>-12,96; 2,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 20,22</t>
+          <t>-37,43; 23,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 10,77</t>
+          <t>-1,93; 11,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 2,8</t>
+          <t>-10,48; 2,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 16,76</t>
+          <t>-28,72; 16,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 15,79</t>
+          <t>6,66; 16,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 13,04</t>
+          <t>4,33; 13,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,98; -4,02</t>
+          <t>-12,89; -3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,47</t>
+          <t>0,8; 9,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,22</t>
+          <t>-4,16; 4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,11; -16,23</t>
+          <t>-29,28; -15,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,39</t>
+          <t>4,95; 11,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,73</t>
+          <t>1,25; 7,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,45; -11,23</t>
+          <t>-19,83; -11,37</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,5; 35,34</t>
+          <t>13,86; 36,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 29,53</t>
+          <t>8,93; 30,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,3; -8,97</t>
+          <t>-26,37; -6,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 15,76</t>
+          <t>1,3; 14,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,89</t>
+          <t>-6,36; 7,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -26,32</t>
+          <t>-44,93; -25,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 21,14</t>
+          <t>8,67; 21,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 14,51</t>
+          <t>2,1; 14,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -20,83</t>
+          <t>-35,26; -21,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,26</t>
+          <t>4,98; 9,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,72</t>
+          <t>1,53; 6,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -5,95</t>
+          <t>-19,03; -6,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,79</t>
+          <t>3,28; 7,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,12</t>
+          <t>-2,29; 2,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -6,66</t>
+          <t>-20,14; -5,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,23</t>
+          <t>4,75; 8,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,71</t>
+          <t>0,3; 3,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -7,64</t>
+          <t>-16,89; -8,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,68; 21,92</t>
+          <t>10,07; 20,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,7</t>
+          <t>3,1; 13,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -12,61</t>
+          <t>-39,72; -13,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,48</t>
+          <t>5,04; 12,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,37</t>
+          <t>-3,54; 3,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -10,23</t>
+          <t>-31,28; -9,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,45; 14,83</t>
+          <t>8,27; 14,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,73</t>
+          <t>0,54; 6,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -13,73</t>
+          <t>-30,06; -14,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-5,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,3</t>
+          <t>-13,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-9,24</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,96</t>
+          <t>5,94; 16,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 9,75</t>
+          <t>-1,45; 9,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 1,9</t>
+          <t>-10,33; 0,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,95</t>
+          <t>1,03; 11,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 7,61</t>
+          <t>-2,92; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -12,12</t>
+          <t>-18,65; -9,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,61</t>
+          <t>5,68; 12,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 7,19</t>
+          <t>-0,2; 6,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,15; -6,5</t>
+          <t>-12,54; -5,76</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-7,96%</t>
+          <t>-10,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-21,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,89%</t>
+          <t>-16,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 37,06</t>
+          <t>12,7; 37,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 20,88</t>
+          <t>-2,83; 20,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 4,31</t>
+          <t>-20,29; 1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,14</t>
+          <t>1,39; 19,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,58</t>
+          <t>-4,39; 12,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,33; -19,95</t>
+          <t>-28,48; -15,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 23,33</t>
+          <t>9,61; 23,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 13,15</t>
+          <t>-0,29; 12,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,39; -12,1</t>
+          <t>-21,85; -10,51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-15,91</t>
+          <t>-8,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,83</t>
+          <t>-16,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,8</t>
+          <t>-12,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,63</t>
+          <t>1,43; 10,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,3</t>
+          <t>-1,52; 7,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -5,79</t>
+          <t>-12,74; -3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,59</t>
+          <t>1,96; 10,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,47</t>
+          <t>-3,6; 4,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,8; -11,66</t>
+          <t>-20,74; -12,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,19</t>
+          <t>2,51; 8,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,07</t>
+          <t>-1,7; 4,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,45; -10,45</t>
+          <t>-15,5; -9,4</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-32,67%</t>
+          <t>-17,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,26%</t>
+          <t>-25,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,48%</t>
+          <t>-21,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 21,21</t>
+          <t>2,81; 22,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 15,61</t>
+          <t>-2,99; 16,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,68; -12,31</t>
+          <t>-25,35; -7,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,85</t>
+          <t>2,9; 16,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,18</t>
+          <t>-5,4; 7,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,35; -18,51</t>
+          <t>-30,79; -19,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,69</t>
+          <t>4,27; 15,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 9,25</t>
+          <t>-2,91; 8,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -18,64</t>
+          <t>-26,39; -16,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,28</t>
+          <t>-9,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,13</t>
+          <t>-20,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-15,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 6,45</t>
+          <t>-4,4; 6,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 4,83</t>
+          <t>-6,47; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -2,01</t>
+          <t>-15,02; -3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,53</t>
+          <t>-0,8; 9,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 1,57</t>
+          <t>-8,43; 1,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 14,65</t>
+          <t>-25,81; -16,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,3</t>
+          <t>-1,26; 6,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 1,36</t>
+          <t>-5,84; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 8,93</t>
+          <t>-18,92; -11,63</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-16,79%</t>
+          <t>-19,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,34%</t>
+          <t>-32,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,79%</t>
+          <t>-27,12%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 14,27</t>
+          <t>-8,37; 14,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 10,26</t>
+          <t>-12,48; 9,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,12; -4,18</t>
+          <t>-28,71; -8,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 13,78</t>
+          <t>-1,34; 14,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 2,57</t>
+          <t>-12,76; 2,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 23,59</t>
+          <t>-39,13; -26,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 11,57</t>
+          <t>-2,15; 11,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 2,51</t>
+          <t>-10,26; 2,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 16,18</t>
+          <t>-32,36; -21,1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,2</t>
+          <t>-10,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-20,75</t>
+          <t>-18,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,71</t>
+          <t>-14,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 16,07</t>
+          <t>6,79; 16,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 13,24</t>
+          <t>4,73; 13,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -3,15</t>
+          <t>-14,49; -5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,03</t>
+          <t>0,76; 9,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,37</t>
+          <t>-4,16; 4,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -15,75</t>
+          <t>-22,42; -14,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,26</t>
+          <t>5,13; 11,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,72</t>
+          <t>0,83; 7,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -11,37</t>
+          <t>-17,59; -11,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-17,66%</t>
+          <t>-22,07%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-32,81%</t>
+          <t>-29,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,62%</t>
+          <t>-26,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 36,95</t>
+          <t>13,6; 36,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 30,21</t>
+          <t>9,65; 30,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,37; -6,98</t>
+          <t>-29,92; -12,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 14,79</t>
+          <t>1,15; 14,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,17</t>
+          <t>-6,3; 7,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,93; -25,58</t>
+          <t>-34,76; -24,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 21,08</t>
+          <t>8,99; 20,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,44</t>
+          <t>1,45; 13,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,26; -21,04</t>
+          <t>-30,95; -21,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>-8,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-15,92</t>
+          <t>-17,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-13,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,73</t>
+          <t>5,07; 9,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,45</t>
+          <t>1,38; 6,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -6,18</t>
+          <t>-11,21; -6,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,81</t>
+          <t>3,14; 7,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,26</t>
+          <t>-2,34; 2,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -5,94</t>
+          <t>-19,68; -15,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,25</t>
+          <t>4,62; 8,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,68</t>
+          <t>0,32; 3,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -8,09</t>
+          <t>-14,76; -11,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-20,84%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-24,93%</t>
+          <t>-27,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-23,03%</t>
+          <t>-23,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,69</t>
+          <t>10,08; 21,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,71</t>
+          <t>2,89; 13,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,72; -13,03</t>
+          <t>-22,63; -13,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,39</t>
+          <t>4,75; 12,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,61</t>
+          <t>-3,62; 3,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -9,37</t>
+          <t>-30,25; -24,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,88</t>
+          <t>8,08; 14,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,71</t>
+          <t>0,62; 6,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -14,5</t>
+          <t>-25,85; -20,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
